--- a/public/templates/coverage/보장분석시트.xlsx
+++ b/public/templates/coverage/보장분석시트.xlsx
@@ -29693,11 +29693,20 @@
       </c>
       <c r="B5" s="798" t="n"/>
       <c r="C5" s="806" t="n"/>
-      <c r="D5" s="807" t="n"/>
+      <c r="D5" s="807">
+        <f>IF(DATEDIF(C4,$T$1,"m")&lt;C5*12,DATEDIF(C4,$T$1,"m"),C5*12)</f>
+        <v/>
+      </c>
       <c r="E5" s="806" t="n"/>
-      <c r="F5" s="807" t="n"/>
+      <c r="F5" s="807">
+        <f>IF(DATEDIF(E4,$T$1,"m")&lt;E5*12,DATEDIF(E4,$T$1,"m"),E5*12)</f>
+        <v/>
+      </c>
       <c r="G5" s="806" t="n"/>
-      <c r="H5" s="807" t="n"/>
+      <c r="H5" s="807">
+        <f>IF(DATEDIF(G4,$T$1,"m")&lt;G5*12,DATEDIF(G4,$T$1,"m"),G5*12)</f>
+        <v/>
+      </c>
       <c r="I5" s="806" t="n"/>
       <c r="J5" s="807">
         <f>IF(DATEDIF(I4,$T$1,"m")&lt;I5*12,DATEDIF(I4,$T$1,"m"),I5*12)</f>
@@ -29818,11 +29827,20 @@
         </is>
       </c>
       <c r="B9" s="803" t="n"/>
-      <c r="C9" s="817" t="n"/>
+      <c r="C9" s="817">
+        <f>C8*C5*12</f>
+        <v/>
+      </c>
       <c r="D9" s="799" t="n"/>
-      <c r="E9" s="817" t="n"/>
+      <c r="E9" s="817">
+        <f>E8*E5*12</f>
+        <v/>
+      </c>
       <c r="F9" s="799" t="n"/>
-      <c r="G9" s="817" t="n"/>
+      <c r="G9" s="817">
+        <f>G8*G5*12</f>
+        <v/>
+      </c>
       <c r="H9" s="799" t="n"/>
       <c r="I9" s="817">
         <f>I8*I5*12</f>
@@ -29863,11 +29881,20 @@
         </is>
       </c>
       <c r="B10" s="803" t="n"/>
-      <c r="C10" s="817" t="n"/>
+      <c r="C10" s="817">
+        <f>C8*D5</f>
+        <v/>
+      </c>
       <c r="D10" s="799" t="n"/>
-      <c r="E10" s="817" t="n"/>
+      <c r="E10" s="817">
+        <f>E8*F5</f>
+        <v/>
+      </c>
       <c r="F10" s="799" t="n"/>
-      <c r="G10" s="817" t="n"/>
+      <c r="G10" s="817">
+        <f>G8*H5</f>
+        <v/>
+      </c>
       <c r="H10" s="799" t="n"/>
       <c r="I10" s="817">
         <f>I8*J5</f>
@@ -29908,11 +29935,20 @@
         </is>
       </c>
       <c r="B11" s="811" t="n"/>
-      <c r="C11" s="817" t="n"/>
+      <c r="C11" s="817">
+        <f>C9-C10</f>
+        <v/>
+      </c>
       <c r="D11" s="799" t="n"/>
-      <c r="E11" s="817" t="n"/>
+      <c r="E11" s="817">
+        <f>E9-E10</f>
+        <v/>
+      </c>
       <c r="F11" s="799" t="n"/>
-      <c r="G11" s="817" t="n"/>
+      <c r="G11" s="817">
+        <f>G9-G10</f>
+        <v/>
+      </c>
       <c r="H11" s="799" t="n"/>
       <c r="I11" s="817">
         <f>I9-I10</f>
@@ -31644,7 +31680,7 @@
       <c r="S60" s="936" t="n"/>
     </row>
     <row r="61" ht="14.1" customHeight="1" s="797">
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>암주요치료비(급여)</t>
         </is>
@@ -31666,7 +31702,7 @@
       <c r="Q61" s="830" t="n"/>
     </row>
     <row r="62" ht="14.1" customHeight="1" s="797">
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>암주요치료비(비급여)</t>
         </is>
@@ -31688,7 +31724,7 @@
       <c r="Q62" s="830" t="n"/>
     </row>
     <row r="63" ht="14.1" customHeight="1" s="797" thickBot="1">
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>뇌심(순환계)주요치료비</t>
         </is>
@@ -33811,7 +33847,7 @@
       <c r="S123" s="980" t="n"/>
     </row>
     <row r="124" ht="14.1" customHeight="1" s="797">
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>암주요치료비(급여)</t>
         </is>
@@ -33831,13 +33867,13 @@
       <c r="O124" s="938" t="n"/>
       <c r="P124" s="837" t="n"/>
       <c r="Q124" s="830" t="n"/>
-      <c r="T124">
+      <c r="T124" s="0">
         <f>T61+C124+E124+G124+I124+K124+M124+O124</f>
         <v/>
       </c>
     </row>
     <row r="125" ht="14.1" customHeight="1" s="797">
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="0" t="inlineStr">
         <is>
           <t>암주요치료비(비급여)</t>
         </is>
@@ -33857,13 +33893,13 @@
       <c r="O125" s="938" t="n"/>
       <c r="P125" s="837" t="n"/>
       <c r="Q125" s="830" t="n"/>
-      <c r="T125">
+      <c r="T125" s="0">
         <f>T62+C125+E125+G125+I125+K125+M125+O125</f>
         <v/>
       </c>
     </row>
     <row r="126" ht="14.1" customHeight="1" s="797" thickBot="1">
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>뇌심(순환계)주요치료비</t>
         </is>
@@ -33883,7 +33919,7 @@
       <c r="O126" s="944" t="n"/>
       <c r="P126" s="846" t="n"/>
       <c r="Q126" s="830" t="n"/>
-      <c r="T126">
+      <c r="T126" s="0">
         <f>T63+C126+E126+G126+I126+K126+M126+O126</f>
         <v/>
       </c>
@@ -63787,9 +63823,9 @@
     <mergeCell ref="P52:Q52"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="P36:P39"/>
+    <mergeCell ref="Q99:R102"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="Q99:R102"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="G62:H62"/>
